--- a/inputs/storage_elevation_table.xlsx
+++ b/inputs/storage_elevation_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\calsim_gits\eis-appendix-gen_upd\eis-appendix-generation\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF324794-CB24-440D-98C9-DCAD92CD021F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C2FA3C-0179-46EC-9FE4-2A215341EC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{B92DCBF1-963B-4AC9-BF86-DA13944A9E5F}"/>
+    <workbookView xWindow="-25020" yWindow="1095" windowWidth="23010" windowHeight="12360" xr2:uid="{B92DCBF1-963B-4AC9-BF86-DA13944A9E5F}"/>
   </bookViews>
   <sheets>
     <sheet name="res_info" sheetId="1" r:id="rId1"/>

--- a/inputs/storage_elevation_table.xlsx
+++ b/inputs/storage_elevation_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\calsim_gits\eis-appendix-gen_upd\eis-appendix-generation\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C2FA3C-0179-46EC-9FE4-2A215341EC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E474C655-304F-42A6-9439-BC407C482718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25020" yWindow="1095" windowWidth="23010" windowHeight="12360" xr2:uid="{B92DCBF1-963B-4AC9-BF86-DA13944A9E5F}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{B92DCBF1-963B-4AC9-BF86-DA13944A9E5F}"/>
   </bookViews>
   <sheets>
     <sheet name="res_info" sheetId="1" r:id="rId1"/>
@@ -265,12 +265,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -285,8 +297,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9390FDB4-AB03-46CA-ADC9-91201B613C80}">
-  <dimension ref="A1:F1008"/>
+  <dimension ref="A1:L1009"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -2717,19 +2731,19 @@
       <c r="A105">
         <v>11</v>
       </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-      <c r="C105">
-        <v>0</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105">
-        <v>0</v>
-      </c>
-      <c r="F105">
+      <c r="B105" s="1">
+        <v>0</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0</v>
+      </c>
+      <c r="D105" s="1">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1">
         <v>4.4389999999999999E-2</v>
       </c>
     </row>
@@ -2737,19 +2751,19 @@
       <c r="A106">
         <v>11</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="1">
         <v>37980</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="1">
         <v>1686</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>14376</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="1">
         <v>326.2</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="1">
         <v>1.304E-2</v>
       </c>
     </row>
@@ -2757,19 +2771,19 @@
       <c r="A107">
         <v>11</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="1">
         <v>142500</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="1">
         <v>3049</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>14376</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="1">
         <v>369.2</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="1">
         <v>6.7799999999999996E-3</v>
       </c>
     </row>
@@ -2777,19 +2791,19 @@
       <c r="A108">
         <v>11</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="1">
         <v>247000</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="1">
         <v>3757</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="1">
         <v>14376</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="1">
         <v>399.6</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="1">
         <v>5.0299999999999997E-3</v>
       </c>
     </row>
@@ -2797,19 +2811,19 @@
       <c r="A109">
         <v>11</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="1">
         <v>356250</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="1">
         <v>4307</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="1">
         <v>14376</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="1">
         <v>426.6</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="1">
         <v>3.6900000000000001E-3</v>
       </c>
     </row>
@@ -2817,19 +2831,19 @@
       <c r="A110">
         <v>11</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="1">
         <v>475000</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="1">
         <v>4745</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="1">
         <v>14376</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="1">
         <v>452.8</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="1">
         <v>2.96E-3</v>
       </c>
     </row>
@@ -2837,19 +2851,19 @@
       <c r="A111">
         <v>11</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="1">
         <v>665000</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="1">
         <v>5307</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="1">
         <v>14376</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="1">
         <v>490.5</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="1">
         <v>2.5500000000000002E-3</v>
       </c>
     </row>
@@ -2857,263 +2871,463 @@
       <c r="A112">
         <v>11</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="1">
         <v>807500</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="1">
         <v>5670</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="1">
         <v>14376</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="1">
         <v>516.4</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="1">
         <v>2.3900000000000002E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>11</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="1">
         <v>902500</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="1">
         <v>5897</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="1">
         <v>14376</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="1">
         <v>532.79999999999995</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="1">
         <v>2.16E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>11</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="1">
         <v>998000</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="1">
         <v>6103</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="1">
         <v>14376</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="1">
         <v>548.70000000000005</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="1">
         <v>2.16E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>12</v>
       </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-      <c r="C115">
-        <v>0</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-      <c r="F115">
+      <c r="B115" s="2">
+        <v>0</v>
+      </c>
+      <c r="C115" s="2">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2">
         <v>4.4380000000000003E-2</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H115">
+        <f>AVERAGE(B115,B105)</f>
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <f t="shared" ref="I115:M124" si="0">AVERAGE(C115,C105)</f>
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <f t="shared" si="0"/>
+        <v>4.4385000000000001E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>12</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="2">
         <v>42000</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="2">
         <v>1864</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="2">
         <v>14376</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="2">
         <v>326.2</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="2">
         <v>1.303E-2</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H116">
+        <f t="shared" ref="H116:H124" si="1">AVERAGE(B116,B106)</f>
+        <v>39990</v>
+      </c>
+      <c r="I116">
+        <f t="shared" si="0"/>
+        <v>1775</v>
+      </c>
+      <c r="J116">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K116">
+        <f t="shared" si="0"/>
+        <v>326.2</v>
+      </c>
+      <c r="L116">
+        <f t="shared" si="0"/>
+        <v>1.3035E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>12</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="2">
         <v>157500</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="2">
         <v>3369</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <v>14376</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="2">
         <v>369.2</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="2">
         <v>6.79E-3</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H117">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I117">
+        <f t="shared" si="0"/>
+        <v>3209</v>
+      </c>
+      <c r="J117">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K117">
+        <f t="shared" si="0"/>
+        <v>369.2</v>
+      </c>
+      <c r="L117">
+        <f t="shared" si="0"/>
+        <v>6.7849999999999994E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>12</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="2">
         <v>273000</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="2">
         <v>4153</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <v>14376</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="2">
         <v>399.6</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="2">
         <v>5.0400000000000002E-3</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H118">
+        <f t="shared" si="1"/>
+        <v>260000</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="0"/>
+        <v>3955</v>
+      </c>
+      <c r="J118">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K118">
+        <f t="shared" si="0"/>
+        <v>399.6</v>
+      </c>
+      <c r="L118">
+        <f t="shared" si="0"/>
+        <v>5.0349999999999995E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>12</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="2">
         <v>393750</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="2">
         <v>4761</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="2">
         <v>14376</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="2">
         <v>426.6</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="2">
         <v>3.6900000000000001E-3</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H119">
+        <f t="shared" si="1"/>
+        <v>375000</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="0"/>
+        <v>4534</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K119">
+        <f t="shared" si="0"/>
+        <v>426.6</v>
+      </c>
+      <c r="L119">
+        <f t="shared" si="0"/>
+        <v>3.6900000000000001E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>12</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="2">
         <v>525000</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="2">
         <v>5245</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="2">
         <v>14376</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="2">
         <v>452.8</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="2">
         <v>2.9499999999999999E-3</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H120">
+        <f t="shared" si="1"/>
+        <v>500000</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="0"/>
+        <v>4995</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K120">
+        <f t="shared" si="0"/>
+        <v>452.8</v>
+      </c>
+      <c r="L120">
+        <f t="shared" si="0"/>
+        <v>2.9550000000000002E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>12</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="2">
         <v>735000</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="2">
         <v>5865</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>14376</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="2">
         <v>490.5</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="2">
         <v>2.5500000000000002E-3</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H121">
+        <f t="shared" si="1"/>
+        <v>700000</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="0"/>
+        <v>5586</v>
+      </c>
+      <c r="J121">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K121">
+        <f t="shared" si="0"/>
+        <v>490.5</v>
+      </c>
+      <c r="L121">
+        <f t="shared" si="0"/>
+        <v>2.5500000000000002E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>12</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="2">
         <v>892500</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="2">
         <v>6266</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="2">
         <v>14376</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="2">
         <v>516.4</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="2">
         <v>2.3999999999999998E-3</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H122">
+        <f t="shared" si="1"/>
+        <v>850000</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="0"/>
+        <v>5968</v>
+      </c>
+      <c r="J122">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K122">
+        <f t="shared" si="0"/>
+        <v>516.4</v>
+      </c>
+      <c r="L122">
+        <f t="shared" si="0"/>
+        <v>2.395E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>12</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="2">
         <v>997500</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="2">
         <v>6518</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="2">
         <v>14376</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="2">
         <v>532.79999999999995</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="2">
         <v>2.1700000000000001E-3</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H123">
+        <f t="shared" si="1"/>
+        <v>950000</v>
+      </c>
+      <c r="I123">
+        <f t="shared" si="0"/>
+        <v>6207.5</v>
+      </c>
+      <c r="J123">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K123">
+        <f t="shared" si="0"/>
+        <v>532.79999999999995</v>
+      </c>
+      <c r="L123">
+        <f t="shared" si="0"/>
+        <v>2.1650000000000003E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>12</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="2">
         <v>1102000</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="2">
         <v>6745</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="2">
         <v>14376</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="2">
         <v>548.70000000000005</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="2">
         <v>2.1700000000000001E-3</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H124">
+        <f t="shared" si="1"/>
+        <v>1050000</v>
+      </c>
+      <c r="I124">
+        <f t="shared" si="0"/>
+        <v>6424</v>
+      </c>
+      <c r="J124">
+        <f t="shared" si="0"/>
+        <v>14376</v>
+      </c>
+      <c r="K124">
+        <f t="shared" si="0"/>
+        <v>548.70000000000005</v>
+      </c>
+      <c r="L124">
+        <f t="shared" si="0"/>
+        <v>2.1650000000000003E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>13</v>
       </c>
@@ -3133,7 +3347,7 @@
         <v>4.4359999999999997E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>13</v>
       </c>
@@ -3153,7 +3367,7 @@
         <v>1.303E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>13</v>
       </c>
@@ -3173,7 +3387,7 @@
         <v>6.79E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>13</v>
       </c>
@@ -20701,6 +20915,18 @@
       </c>
       <c r="E1008">
         <v>548.70000000000005</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1009">
+        <v>999</v>
+      </c>
+      <c r="B1009">
+        <f>1200000*2</f>
+        <v>2400000</v>
+      </c>
+      <c r="E1009">
+        <v>581.20000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/storage_elevation_table.xlsx
+++ b/inputs/storage_elevation_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\calsim_gits\eis-appendix-gen_upd\eis-appendix-generation\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\20251211_BA_Modeling_Appendix\EIS_Appendix_Generation\EIS-Appendix-Generation-main\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E474C655-304F-42A6-9439-BC407C482718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193B1E74-B48A-4653-BEA9-9C206E517E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{B92DCBF1-963B-4AC9-BF86-DA13944A9E5F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B92DCBF1-963B-4AC9-BF86-DA13944A9E5F}"/>
   </bookViews>
   <sheets>
     <sheet name="res_info" sheetId="1" r:id="rId1"/>
@@ -636,18 +636,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9390FDB4-AB03-46CA-ADC9-91201B613C80}">
   <dimension ref="A1:L1009"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +667,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -687,7 +687,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -707,7 +707,7 @@
         <v>7.8600000000000007E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -727,7 +727,7 @@
         <v>6.79E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -747,7 +747,7 @@
         <v>6.6699999999999997E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -767,7 +767,7 @@
         <v>6.1900000000000002E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -787,7 +787,7 @@
         <v>5.6299999999999996E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -807,7 +807,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -827,7 +827,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -847,7 +847,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -867,7 +867,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -887,7 +887,7 @@
         <v>3.8460000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3</v>
       </c>
@@ -907,7 +907,7 @@
         <v>1.9230000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>3</v>
       </c>
@@ -927,7 +927,7 @@
         <v>1.538E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>3</v>
       </c>
@@ -947,7 +947,7 @@
         <v>1.316E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -967,7 +967,7 @@
         <v>7.6899999999999998E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>3</v>
       </c>
@@ -987,7 +987,7 @@
         <v>1.154E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>7.6899999999999998E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>1.026E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>5.8799999999999998E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>5.8799999999999998E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>4</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>4</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>4</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>9.0100000000000006E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>8.0499999999999999E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>6.1799999999999997E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>5.79E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>4</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>5.3400000000000001E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>4</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>4.2900000000000004E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>4</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>3.3600000000000001E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>4</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>5.1700000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>5.1700000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>5</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>5</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>5</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>3.3329999999999999E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>5</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>5</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>5.8180000000000003E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>5</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>3.1050000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>5</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>5</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>2.4729999999999999E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>5</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>1.7160000000000002E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>5</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>1.7160000000000002E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>6</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>2.0039999999999999E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>6</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>1.061E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>6</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>6.6600000000000001E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>6</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>5.0800000000000003E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>6</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>4.81E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>6</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>4.5700000000000003E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>6</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>4.15E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>6</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>3.7399999999999998E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>6</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>3.3300000000000001E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>6</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>3.3600000000000001E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>6</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>3.3600000000000001E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>7</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>7</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>0.13485</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>7</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>6.5790000000000001E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>7</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>7.1709999999999996E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>7</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>7</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>7</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>7</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>2.869E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>7</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>3.3119999999999997E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>7</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>3.3119999999999997E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>8</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>0.18182000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>8</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>2.6880000000000001E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>8</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>1.7489999999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>8</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>1.7899999999999999E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>8</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>2.052E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>8</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>1.839E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>8</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>1.443E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>1.2239999999999999E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>9.4199999999999996E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>5.9199999999999999E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>4.9300000000000004E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>8</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>4.9300000000000004E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>9</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>9.7110000000000002E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>9</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>5.6259999999999998E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>9</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>4.947E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>9</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>4.7449999999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>9</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>4.326E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>9</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>4.5449999999999997E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>9</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>4.2250000000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>9</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>5.1279999999999999E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>9</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>5.747E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>9</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>6.8690000000000001E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>9</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>9</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>10</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>6.2560000000000004E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>10</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>2.1850000000000001E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>10</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>2.1770000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>10</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>1.085E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>10</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>1.085E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>10</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>7.7099999999999998E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>10</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>7.7200000000000003E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>10</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>7.7099999999999998E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>10</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>6.2100000000000002E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>10</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>5.5599999999999998E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>10</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>4.3699999999999998E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>10</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>3.6099999999999999E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>10</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>3.29E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>10</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>3.3300000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>10</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>3.5500000000000002E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>10</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>3.5500000000000002E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>11</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>4.4389999999999999E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>11</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>1.304E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>11</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>6.7799999999999996E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>11</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>5.0299999999999997E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>11</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>3.6900000000000001E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>11</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2.96E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>11</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2.5500000000000002E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>11</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>2.3900000000000002E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>11</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>2.16E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>11</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>2.16E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>12</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <f t="shared" ref="I115:M124" si="0">AVERAGE(C115,C105)</f>
+        <f t="shared" ref="I115:L124" si="0">AVERAGE(C115,C105)</f>
         <v>0</v>
       </c>
       <c r="J115">
@@ -2967,7 +2967,7 @@
         <v>4.4385000000000001E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>12</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>1.3035E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>12</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>6.7849999999999994E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>12</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>5.0349999999999995E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>12</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>3.6900000000000001E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>12</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>2.9550000000000002E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>12</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>2.5500000000000002E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>12</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>2.395E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>12</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>2.1650000000000003E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>12</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>2.1650000000000003E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>13</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>4.4359999999999997E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>13</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>1.303E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>13</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>6.79E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>13</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>5.0400000000000002E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>13</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>3.6900000000000001E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>13</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>2.9499999999999999E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>13</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>2.5500000000000002E-3</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>13</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>13</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>2.1700000000000001E-3</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>13</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>1.0499999999999999E-3</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>13</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>1.0499999999999999E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>15</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>4.6730000000000001E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>15</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>1.9859999999999999E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>15</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>1.6379999999999999E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>15</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>1.167E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>15</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>15</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>15</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>15</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>15</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>15</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>9.4599999999999997E-3</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>15</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>9.4599999999999997E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>16</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>2.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>16</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>1.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>16</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>1.9099999999999999E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>16</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>1.95E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>16</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>1.9709999999999998E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>16</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>1.9820000000000001E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>16</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>16</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>16</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>16</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>17</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>1.5859999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>17</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>1.5859999999999999E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>18</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>2.0080000000000001E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>18</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>1.3599999999999999E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>18</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>1.128E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>18</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>9.7000000000000003E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>18</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>8.4200000000000004E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>18</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>7.45E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>18</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>6.6600000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>18</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>6.0099999999999997E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>18</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>5.4900000000000001E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>18</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>5.4900000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>19</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>19</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>19</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>19</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>19</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>19</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>19</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>19</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>19</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>19</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>20</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>1.3679999999999999E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>20</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>7.8799999999999999E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>20</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>6.96E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>20</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>6.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>20</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>6.0299999999999998E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>20</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>5.8100000000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>20</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>5.6299999999999996E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>20</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>5.5100000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>20</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>20</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>21</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>21</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>21</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>21</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>21</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>21</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>21</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>21</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>21</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>21</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>22</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>2.1479999999999999E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>22</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>1.3849999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>22</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>1.47E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>22</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>22</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>6.5700000000000003E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>22</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>4.3099999999999996E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>22</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>3.4399999999999999E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>22</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>3.15E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>22</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>2.9499999999999999E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>22</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>2.9499999999999999E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>23</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>23</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>7.8799999999999999E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>23</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>6.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>23</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>5.64E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>23</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>5.3200000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>23</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>5.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>23</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>4.9399999999999999E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>23</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>4.8300000000000001E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>23</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>4.7299999999999998E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>23</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>4.7299999999999998E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>24</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>24</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>24</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>24</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>24</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>24</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>24</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>24</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>24</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>24</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>25</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>25</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>3.1669999999999997E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>25</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>25</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>1.6670000000000001E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>25</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>1.238E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>25</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>1.917E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>25</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>9.5999999999999992E-3</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>25</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>8.1700000000000002E-3</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>25</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>5.9800000000000001E-3</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>25</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>5.9800000000000001E-3</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>26</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>1.1610000000000001E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>26</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>6.6100000000000004E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>26</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>5.7099999999999998E-3</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>26</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>4.1999999999999997E-3</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>26</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>3.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>26</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>26</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>26</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>26</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>26</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>27</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>0.11749999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>27</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>3.5090000000000003E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>27</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>2.3290000000000002E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>27</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>1.8950000000000002E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>27</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>1.5650000000000001E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>27</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>1.583E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>27</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>27</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>1.371E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>27</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>1.231E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>27</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>27</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>28</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>28</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>3.1820000000000001E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>28</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>1.333E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>28</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>8.2699999999999996E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>28</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>6.0499999999999998E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>28</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>5.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>28</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>4.7200000000000002E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>28</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>4.96E-3</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>28</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>5.0299999999999997E-3</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>28</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>5.3099999999999996E-3</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>28</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>5.3099999999999996E-3</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>29</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>29</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>2.333E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>29</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>29</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>8.77E-3</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>29</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>5.8399999999999997E-3</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>29</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>4.8199999999999996E-3</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>29</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>1.8290000000000001E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>29</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>1.6820000000000002E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>29</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>1.6820000000000002E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>29</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>1.6820000000000002E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>30</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>0.17241000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>30</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>7.5469999999999995E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>30</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>0.10874</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>30</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>6.3750000000000001E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>30</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>3.7379999999999997E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>30</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>2.3140000000000001E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>30</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>1.6230000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>30</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>1.0449999999999999E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>30</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>8.4100000000000008E-3</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>30</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>8.3899999999999999E-3</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>30</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>5.9199999999999999E-3</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>30</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>4.8700000000000002E-3</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>30</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>4.2599999999999999E-3</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>30</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>30</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>3.2100000000000002E-3</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>30</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>2.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>30</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>2.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>31</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>8.2000000000000007E-3</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>31</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>5.3699999999999998E-3</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>31</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>31</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>31</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>4.1700000000000001E-3</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>31</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>31</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>2.1430000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>31</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>31</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>32</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>1.4710000000000001E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>32</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>1.4710000000000001E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>32</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>1.47E-2</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>32</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>1.4670000000000001E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>32</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>1.4670000000000001E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>33</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>1.2149999999999999E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>33</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>1.21E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>33</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>1.2330000000000001E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>33</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>1.192E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>33</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>1.192E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>34</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>1.533E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>34</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>1.533E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>35</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>35</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>5.3E-3</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>35</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>9.3600000000000003E-3</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>35</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>9.3100000000000006E-3</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>35</v>
       </c>
@@ -7307,7 +7307,7 @@
         <v>9.3100000000000006E-3</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>36</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>1.4800000000000001E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>36</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>1.4800000000000001E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>37</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>37</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>37</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>1.9000000000000001E-4</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>37</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>1.9000000000000001E-4</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>40</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>1.82796</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>40</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>0.14069999999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>40</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>40</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>8.8889999999999997E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>40</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>7.3270000000000002E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>40</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>6.166E-2</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>40</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>5.0849999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>40</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>4.4069999999999998E-2</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>40</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>3.9600000000000003E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>40</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>3.7719999999999997E-2</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>40</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>3.508E-2</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>40</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>3.0179999999999998E-2</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>40</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>2.7320000000000001E-2</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>40</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>2.3910000000000001E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>40</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>2.2030000000000001E-2</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>40</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>2.2950000000000002E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>40</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>1.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>40</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>2.0240000000000001E-2</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>40</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>2.102E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>40</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>1.9879999999999998E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>40</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>1.8630000000000001E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>40</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>1.77E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>40</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>1.77E-2</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>41</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>41</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>0.20408000000000001</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>41</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>0.1134</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>41</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>0.15115999999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>41</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>9.06E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>41</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>9.4939999999999997E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>41</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>6.7049999999999998E-2</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>41</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>6.3149999999999998E-2</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>41</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>4.7280000000000003E-2</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>41</v>
       </c>
@@ -8087,7 +8087,7 @@
         <v>3.8830000000000003E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>41</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>3.3079999999999998E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>41</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>3.7629999999999997E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>41</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>3.0970000000000001E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>41</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>2.6499999999999999E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>41</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>2.393E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>41</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>2.3609999999999999E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>41</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>2.0459999999999999E-2</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>41</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>4.965E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>41</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>1.7909999999999999E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>41</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>41</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>1.626E-2</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>41</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>1.6049999999999998E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>41</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>1.4579999999999999E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>41</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>1.396E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>41</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>1.37E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>41</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>1.499E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>41</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>1.223E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>41</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>1.223E-2</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>41</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>1.223E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>42</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>0.15028</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>42</v>
       </c>
@@ -8507,7 +8507,7 @@
         <v>0.15028</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>42</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>42</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>8.4059999999999996E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>42</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>8.2900000000000001E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>42</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>6.0979999999999999E-2</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>42</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>4.6240000000000003E-2</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>42</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>4.5589999999999999E-2</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>42</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>4.7050000000000002E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>42</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>5.1499999999999997E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>42</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>3.585E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>42</v>
       </c>
@@ -8707,7 +8707,7 @@
         <v>3.2059999999999998E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>42</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>3.2570000000000002E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>42</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>2.503E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>42</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>1.821E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>42</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>1.865E-2</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>42</v>
       </c>
@@ -8807,7 +8807,7 @@
         <v>1.8120000000000001E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>42</v>
       </c>
@@ -8827,7 +8827,7 @@
         <v>1.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>42</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>1.5350000000000001E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>42</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>1.359E-2</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>42</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>1.3599999999999999E-2</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>42</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>1.3599999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>44</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>3.3600000000000001E-3</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>44</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>3.3600000000000001E-3</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>44</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>5.0299999999999997E-3</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>44</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>44</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>45</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>5.3499999999999999E-2</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>45</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>5.3499999999999999E-2</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>45</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>3.27E-2</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>45</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>2.9600000000000001E-2</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>45</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>45</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>3.73E-2</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>45</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>3.9399999999999998E-2</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>45</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>3.3799999999999997E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>45</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>45</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>45</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>45</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>45</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>1.5100000000000001E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>45</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>45</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>1.04E-2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>45</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>9.7000000000000003E-3</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>45</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>8.3999999999999995E-3</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>45</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>45</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>6.3E-3</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>45</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>45</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>5.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>45</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>4.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>52</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>4.65E-2</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>52</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>52</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>1.84E-2</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>52</v>
       </c>
@@ -9527,7 +9527,7 @@
         <v>1.52E-2</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>52</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>1.3100000000000001E-2</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>52</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>1.14E-2</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>52</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>9.75E-3</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>52</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>8.1499999999999993E-3</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>52</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>6.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>52</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>6.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>53</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>3.8870000000000002E-2</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>53</v>
       </c>
@@ -9687,7 +9687,7 @@
         <v>1.5350000000000001E-2</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>53</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>1.072E-2</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>53</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>8.4799999999999997E-3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>53</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>7.1199999999999996E-3</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>53</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>6.2399999999999999E-3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>53</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>5.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>53</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>5.1200000000000004E-3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>53</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>4.7200000000000002E-3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>53</v>
       </c>
@@ -9847,7 +9847,7 @@
         <v>4.7200000000000002E-3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>63</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>1.1610000000000001E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>63</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>6.6100000000000004E-3</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>63</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>5.7099999999999998E-3</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>63</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>4.1999999999999997E-3</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>63</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>3.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>63</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>63</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>63</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>63</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>63</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>74</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>0.25142999999999999</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>74</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>0.23638000000000001</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>74</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>0.15195</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>74</v>
       </c>
@@ -10127,7 +10127,7 @@
         <v>0.10036</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>74</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>4.8590000000000001E-2</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>74</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>4.2860000000000002E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>74</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>4.2860000000000002E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>75</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>6.5079999999999999E-2</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>75</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>5.8139999999999997E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>75</v>
       </c>
@@ -10247,7 +10247,7 @@
         <v>6.9379999999999997E-2</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>75</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>75</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>0.12435</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>75</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>0.12435</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>76</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>2.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>76</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>1.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>76</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>1.9099999999999999E-2</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>76</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>1.95E-2</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>76</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>1.9709999999999998E-2</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>76</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>1.9820000000000001E-2</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>76</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>76</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>76</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>76</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>78</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>0.48332999999999998</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>78</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>0.12143</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>78</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>0.10833</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>78</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>9.4439999999999996E-2</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>78</v>
       </c>
@@ -10607,7 +10607,7 @@
         <v>8.6360000000000006E-2</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>78</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>8.0769999999999995E-2</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>78</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>7.4190000000000006E-2</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>78</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>6.2859999999999999E-2</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>78</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>78</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>0.36303999999999997</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>78</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>0.36303999999999997</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>79</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>0.29143999999999998</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>79</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>0.11706</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>79</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>7.9649999999999999E-2</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>79</v>
       </c>
@@ -10807,7 +10807,7 @@
         <v>6.7119999999999999E-2</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>79</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>6.1100000000000002E-2</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>79</v>
       </c>
@@ -10847,7 +10847,7 @@
         <v>5.1990000000000001E-2</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>79</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>4.3049999999999998E-2</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>79</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>3.7109999999999997E-2</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>79</v>
       </c>
@@ -10907,7 +10907,7 @@
         <v>3.2939999999999997E-2</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>79</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>3.2939999999999997E-2</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>81</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>81</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>7.8799999999999999E-3</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>81</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>6.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>81</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>5.64E-3</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>81</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>5.3200000000000001E-3</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>81</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>5.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>81</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>4.9399999999999999E-3</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>81</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>4.8300000000000001E-3</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>81</v>
       </c>
@@ -11107,7 +11107,7 @@
         <v>4.7299999999999998E-3</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>81</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>4.7299999999999998E-3</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>90</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>0.32154882200000001</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>90</v>
       </c>
@@ -11167,7 +11167,7 @@
         <v>3.1091718000000001E-2</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>90</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>1.8058780999999999E-2</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>90</v>
       </c>
@@ -11207,7 +11207,7 @@
         <v>1.7928989999999999E-2</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>90</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>1.7007650999999999E-2</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>90</v>
       </c>
@@ -11247,7 +11247,7 @@
         <v>1.9146630000000001E-2</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>90</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>2.2082747999999999E-2</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>90</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>1.7866381000000001E-2</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>90</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>7.9255469999999998E-3</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>90</v>
       </c>
@@ -11327,7 +11327,7 @@
         <v>1.4440069E-2</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>90</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>1.3830761E-2</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>90</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>1.4408809999999999E-2</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>90</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>1.4494763000000001E-2</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>90</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>1.4390426E-2</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>90</v>
       </c>
@@ -11427,7 +11427,7 @@
         <v>1.4078573E-2</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>90</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>1.4337676000000001E-2</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>90</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>1.4757574000000001E-2</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>90</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>1.4403401999999999E-2</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>90</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>1.3985562E-2</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>90</v>
       </c>
@@ -11527,7 +11527,7 @@
         <v>1.3736091000000001E-2</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>90</v>
       </c>
@@ -11547,7 +11547,7 @@
         <v>1.425071E-2</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>90</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>1.369506E-2</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>90</v>
       </c>
@@ -11587,7 +11587,7 @@
         <v>1.4505903000000001E-2</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>90</v>
       </c>
@@ -11607,7 +11607,7 @@
         <v>1.4637414E-2</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>90</v>
       </c>
@@ -11627,7 +11627,7 @@
         <v>1.3363319E-2</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>90</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>1.3207986E-2</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>90</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>1.3132570999999999E-2</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>90</v>
       </c>
@@ -11687,7 +11687,7 @@
         <v>1.3304768E-2</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>90</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>1.3481526000000001E-2</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>90</v>
       </c>
@@ -11727,7 +11727,7 @@
         <v>1.3215024000000001E-2</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>90</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>1.3166636000000001E-2</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>90</v>
       </c>
@@ -11767,7 +11767,7 @@
         <v>1.3211428000000001E-2</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>90</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>1.3007233999999999E-2</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>90</v>
       </c>
@@ -11807,7 +11807,7 @@
         <v>1.2706556000000001E-2</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>90</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>1.2735998E-2</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>90</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>1.273736E-2</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>90</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>1.2835353000000001E-2</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>90</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>1.3115432999999999E-2</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>90</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>1.3105973999999999E-2</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>90</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>1.3407334999999999E-2</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>90</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>1.3563937E-2</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>90</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>1.3886506999999999E-2</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>90</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>1.2784613E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>90</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>1.310001E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>90</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>1.2740669E-2</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>90</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>1.3768156E-2</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>90</v>
       </c>
@@ -12067,7 +12067,7 @@
         <v>1.3848890000000001E-2</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>90</v>
       </c>
@@ -12087,7 +12087,7 @@
         <v>1.3415131E-2</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>90</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>1.4045515999999999E-2</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>90</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>1.2621755E-2</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>90</v>
       </c>
@@ -12147,7 +12147,7 @@
         <v>1.3804454000000001E-2</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>90</v>
       </c>
@@ -12167,7 +12167,7 @@
         <v>1.2497581000000001E-2</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>90</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>1.1631944E-2</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>90</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>1.202863E-2</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>90</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>1.2262818E-2</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>90</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>1.2178812000000001E-2</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>90</v>
       </c>
@@ -12267,7 +12267,7 @@
         <v>1.1139685999999999E-2</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>90</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>1.1577489999999999E-2</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>90</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>1.1310156E-2</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>90</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>1.1150808E-2</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>90</v>
       </c>
@@ -12347,7 +12347,7 @@
         <v>1.0856275E-2</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>90</v>
       </c>
@@ -12367,7 +12367,7 @@
         <v>1.0685264999999999E-2</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>90</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>1.0177591E-2</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>90</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>1.0252826E-2</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>90</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>1.0616297E-2</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>90</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>9.9911180000000002E-3</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>90</v>
       </c>
@@ -12467,7 +12467,7 @@
         <v>4.6854979999999997E-3</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>90</v>
       </c>
@@ -12487,7 +12487,7 @@
         <v>9.1162199999999995E-3</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>90</v>
       </c>
@@ -12507,7 +12507,7 @@
         <v>9.0738069999999997E-3</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>90</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>8.9270840000000001E-3</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>90</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>8.8817870000000004E-3</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>90</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>9.0393509999999993E-3</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>90</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>8.6778949999999997E-3</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>90</v>
       </c>
@@ -12607,7 +12607,7 @@
         <v>8.3768379999999993E-3</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>90</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>8.9742490000000001E-3</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>90</v>
       </c>
@@ -12647,7 +12647,7 @@
         <v>8.1173649999999997E-3</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>90</v>
       </c>
@@ -12667,7 +12667,7 @@
         <v>8.4623939999999998E-3</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>90</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>7.9969770000000006E-3</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>90</v>
       </c>
@@ -12707,7 +12707,7 @@
         <v>7.6788739999999996E-3</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>90</v>
       </c>
@@ -12727,7 +12727,7 @@
         <v>7.7643340000000003E-3</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>90</v>
       </c>
@@ -12747,7 +12747,7 @@
         <v>7.7956969999999999E-3</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>90</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>7.5163440000000003E-3</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>90</v>
       </c>
@@ -12787,7 +12787,7 @@
         <v>7.6722489999999999E-3</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>90</v>
       </c>
@@ -12807,7 +12807,7 @@
         <v>7.7859280000000001E-3</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>90</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>7.8195769999999994E-3</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>90</v>
       </c>
@@ -12847,7 +12847,7 @@
         <v>7.671906E-3</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>90</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>7.9757219999999993E-3</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>90</v>
       </c>
@@ -12887,7 +12887,7 @@
         <v>7.7366370000000002E-3</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>90</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>8.0513879999999996E-3</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>90</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>1.2210623E-2</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>90</v>
       </c>
@@ -12947,7 +12947,7 @@
         <v>8.1852320000000006E-3</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>90</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>9.1658899999999995E-3</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>90</v>
       </c>
@@ -12987,7 +12987,7 @@
         <v>7.6297489999999999E-3</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>90</v>
       </c>
@@ -13007,7 +13007,7 @@
         <v>7.3207159999999997E-3</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>90</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>6.7108109999999997E-3</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>90</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>6.5269170000000001E-3</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>90</v>
       </c>
@@ -13067,7 +13067,7 @@
         <v>1.6916012000000001E-2</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>90</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>1.6916012000000001E-2</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>91</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>0.14252336400000001</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>91</v>
       </c>
@@ -13127,7 +13127,7 @@
         <v>0.136690647</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>91</v>
       </c>
@@ -13147,7 +13147,7 @@
         <v>0.16931216900000001</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>91</v>
       </c>
@@ -13167,7 +13167,7 @@
         <v>0.17228464399999999</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>91</v>
       </c>
@@ -13187,7 +13187,7 @@
         <v>0.159151194</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>91</v>
       </c>
@@ -13207,7 +13207,7 @@
         <v>0.12903225800000001</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>91</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>0.101788171</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>91</v>
       </c>
@@ -13247,7 +13247,7 @@
         <v>7.2277227999999999E-2</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>91</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>5.291411E-2</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>91</v>
       </c>
@@ -13287,7 +13287,7 @@
         <v>4.2763158000000003E-2</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>91</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>3.7712895000000003E-2</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>91</v>
       </c>
@@ -13327,7 +13327,7 @@
         <v>4.3899290000000001E-2</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>91</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>4.9136786000000002E-2</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>91</v>
       </c>
@@ -13367,7 +13367,7 @@
         <v>4.0779062999999997E-2</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>91</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>4.2505593000000001E-2</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>91</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>3.1754295000000002E-2</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>91</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>2.6600985000000001E-2</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>91</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>2.9725964000000001E-2</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>91</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>2.8033289999999999E-2</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>91</v>
       </c>
@@ -13487,7 +13487,7 @@
         <v>2.4583332999999999E-2</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>91</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>2.8379976000000001E-2</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>91</v>
       </c>
@@ -13527,7 +13527,7 @@
         <v>3.0392883999999998E-2</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>91</v>
       </c>
@@ -13547,7 +13547,7 @@
         <v>3.0651340999999999E-2</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>91</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>2.7595268999999999E-2</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>91</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>2.5257249999999998E-2</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>91</v>
       </c>
@@ -13607,7 +13607,7 @@
         <v>2.4621773999999999E-2</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>91</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>2.3479491000000002E-2</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>91</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>2.2156174000000001E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>91</v>
       </c>
@@ -13667,7 +13667,7 @@
         <v>2.3213825E-2</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>91</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>2.4342267000000001E-2</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>91</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>2.8139535E-2</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>91</v>
       </c>
@@ -13727,7 +13727,7 @@
         <v>3.0010953E-2</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>91</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>3.1449126000000001E-2</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>91</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>2.9588086999999999E-2</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>91</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>2.9336734999999999E-2</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>91</v>
       </c>
@@ -13807,7 +13807,7 @@
         <v>2.6882646999999999E-2</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>91</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>2.7555844999999999E-2</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>91</v>
       </c>
@@ -13847,7 +13847,7 @@
         <v>2.5065759E-2</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>91</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>2.3872679000000001E-2</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>91</v>
       </c>
@@ -13887,7 +13887,7 @@
         <v>2.3046654999999999E-2</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>91</v>
       </c>
@@ -13907,7 +13907,7 @@
         <v>2.2290854999999998E-2</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>91</v>
       </c>
@@ -13927,7 +13927,7 @@
         <v>2.0970024E-2</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>91</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>1.9527869999999999E-2</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>91</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>1.7403742999999999E-2</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>91</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>1.7044799999999999E-2</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>91</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>1.7030276E-2</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>91</v>
       </c>
@@ -14027,7 +14027,7 @@
         <v>1.6356397000000002E-2</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>91</v>
       </c>
@@ -14047,7 +14047,7 @@
         <v>1.6145832999999998E-2</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>91</v>
       </c>
@@ -14067,7 +14067,7 @@
         <v>1.5837789000000001E-2</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>91</v>
       </c>
@@ -14087,7 +14087,7 @@
         <v>1.4392011E-2</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>91</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>1.4085848E-2</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>91</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>1.4059754000000001E-2</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>91</v>
       </c>
@@ -14147,7 +14147,7 @@
         <v>1.3323731E-2</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>91</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>1.3578625E-2</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>91</v>
       </c>
@@ -14187,7 +14187,7 @@
         <v>1.3219616E-2</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>91</v>
       </c>
@@ -14207,7 +14207,7 @@
         <v>1.2549866999999999E-2</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>91</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>1.1287965E-2</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>91</v>
       </c>
@@ -14247,7 +14247,7 @@
         <v>1.0961950999999999E-2</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>91</v>
       </c>
@@ -14267,7 +14267,7 @@
         <v>1.0114369999999999E-2</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>91</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>9.9893240000000008E-3</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>91</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>9.4981679999999995E-3</v>
       </c>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>91</v>
       </c>
@@ -14327,7 +14327,7 @@
         <v>9.2483849999999996E-3</v>
       </c>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>91</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>9.081736E-3</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>91</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>9.3378609999999994E-3</v>
       </c>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>91</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>9.3036170000000001E-3</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>91</v>
       </c>
@@ -14407,7 +14407,7 @@
         <v>9.4699550000000004E-3</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>91</v>
       </c>
@@ -14427,7 +14427,7 @@
         <v>8.4342989999999993E-3</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>91</v>
       </c>
@@ -14447,7 +14447,7 @@
         <v>8.2954770000000008E-3</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>91</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>7.9678690000000007E-3</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>91</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>8.1585819999999993E-3</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>91</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>8.4607669999999992E-3</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>91</v>
       </c>
@@ -14527,7 +14527,7 @@
         <v>8.2588599999999998E-3</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>91</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>4.324194E-3</v>
       </c>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>91</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>4.324194E-3</v>
       </c>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>92</v>
       </c>
@@ -14587,7 +14587,7 @@
         <v>3.5479999999999998E-2</v>
       </c>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>92</v>
       </c>
@@ -14607,7 +14607,7 @@
         <v>1.788E-2</v>
       </c>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>92</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>1.418E-2</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>92</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>1.222E-2</v>
       </c>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>92</v>
       </c>
@@ -14667,7 +14667,7 @@
         <v>1.095E-2</v>
       </c>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>92</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>1.0030000000000001E-2</v>
       </c>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>92</v>
       </c>
@@ -14707,7 +14707,7 @@
         <v>9.3200000000000002E-3</v>
       </c>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>92</v>
       </c>
@@ -14727,7 +14727,7 @@
         <v>8.7399999999999995E-3</v>
       </c>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>92</v>
       </c>
@@ -14747,7 +14747,7 @@
         <v>8.3099999999999997E-3</v>
       </c>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>92</v>
       </c>
@@ -14767,7 +14767,7 @@
         <v>7.9100000000000004E-3</v>
       </c>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>92</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>7.9100000000000004E-3</v>
       </c>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>93</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>1.01E-2</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>93</v>
       </c>
@@ -14827,7 +14827,7 @@
         <v>5.8700000000000002E-3</v>
       </c>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A700">
         <v>93</v>
       </c>
@@ -14847,7 +14847,7 @@
         <v>4.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>93</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>3.9699999999999996E-3</v>
       </c>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>93</v>
       </c>
@@ -14887,7 +14887,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>93</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>3.49E-3</v>
       </c>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>93</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>3.4399999999999999E-3</v>
       </c>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>93</v>
       </c>
@@ -14947,7 +14947,7 @@
         <v>3.4399999999999999E-3</v>
       </c>
     </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>93</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A707">
         <v>93</v>
       </c>
@@ -14987,7 +14987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>94</v>
       </c>
@@ -15007,7 +15007,7 @@
         <v>1.0070000000000001E-2</v>
       </c>
     </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>94</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>0.59191000000000005</v>
       </c>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>94</v>
       </c>
@@ -15047,7 +15047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>94</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>9.2499999999999995E-3</v>
       </c>
     </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>94</v>
       </c>
@@ -15087,7 +15087,7 @@
         <v>1.8020000000000001E-2</v>
       </c>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>94</v>
       </c>
@@ -15107,7 +15107,7 @@
         <v>2.3869999999999999E-2</v>
       </c>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>94</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>2.1409999999999998E-2</v>
       </c>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>94</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>94</v>
       </c>
@@ -15167,7 +15167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A717">
         <v>94</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>1.6100000000000001E-3</v>
       </c>
     </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>94</v>
       </c>
@@ -15207,7 +15207,7 @@
         <v>1.5100000000000001E-2</v>
       </c>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>94</v>
       </c>
@@ -15227,7 +15227,7 @@
         <v>2.07E-2</v>
       </c>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>94</v>
       </c>
@@ -15247,7 +15247,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>94</v>
       </c>
@@ -15267,7 +15267,7 @@
         <v>1.618E-2</v>
       </c>
     </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>94</v>
       </c>
@@ -15287,7 +15287,7 @@
         <v>1.669E-2</v>
       </c>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>94</v>
       </c>
@@ -15307,7 +15307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A724">
         <v>94</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A725">
         <v>94</v>
       </c>
@@ -15347,7 +15347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>94</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>1.038E-2</v>
       </c>
     </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>94</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>1.375E-2</v>
       </c>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>94</v>
       </c>
@@ -15407,7 +15407,7 @@
         <v>1.7420000000000001E-2</v>
       </c>
     </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>94</v>
       </c>
@@ -15427,7 +15427,7 @@
         <v>1.8460000000000001E-2</v>
       </c>
     </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>94</v>
       </c>
@@ -15447,7 +15447,7 @@
         <v>1.528E-2</v>
       </c>
     </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>94</v>
       </c>
@@ -15467,7 +15467,7 @@
         <v>3.7100000000000002E-3</v>
       </c>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>94</v>
       </c>
@@ -15487,7 +15487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>94</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>94</v>
       </c>
@@ -15527,7 +15527,7 @@
         <v>7.3899999999999999E-3</v>
       </c>
     </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A735">
         <v>94</v>
       </c>
@@ -15547,7 +15547,7 @@
         <v>1.464E-2</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A736">
         <v>94</v>
       </c>
@@ -15567,7 +15567,7 @@
         <v>1.7489999999999999E-2</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A737">
         <v>94</v>
       </c>
@@ -15587,7 +15587,7 @@
         <v>1.524E-2</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>94</v>
       </c>
@@ -15607,7 +15607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>94</v>
       </c>
@@ -15627,7 +15627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>94</v>
       </c>
@@ -15647,7 +15647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A741">
         <v>94</v>
       </c>
@@ -15667,7 +15667,7 @@
         <v>1.124E-2</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>94</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>9.3399999999999993E-3</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>94</v>
       </c>
@@ -15707,7 +15707,7 @@
         <v>1.5480000000000001E-2</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>95</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>4.1669999999999999E-2</v>
       </c>
     </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A745">
         <v>95</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>95</v>
       </c>
@@ -15767,7 +15767,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>95</v>
       </c>
@@ -15787,7 +15787,7 @@
         <v>3.0630000000000001E-2</v>
       </c>
     </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>95</v>
       </c>
@@ -15807,7 +15807,7 @@
         <v>2.0959999999999999E-2</v>
       </c>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>95</v>
       </c>
@@ -15827,7 +15827,7 @@
         <v>2.4580000000000001E-2</v>
       </c>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>95</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>2.3730000000000001E-2</v>
       </c>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>95</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>2.1430000000000001E-2</v>
       </c>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>95</v>
       </c>
@@ -15887,7 +15887,7 @@
         <v>1.2760000000000001E-2</v>
       </c>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>95</v>
       </c>
@@ -15907,7 +15907,7 @@
         <v>8.1099999999999992E-3</v>
       </c>
     </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>95</v>
       </c>
@@ -15927,7 +15927,7 @@
         <v>6.3200000000000001E-3</v>
       </c>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>95</v>
       </c>
@@ -15947,7 +15947,7 @@
         <v>1.281E-2</v>
       </c>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A756">
         <v>96</v>
       </c>
@@ -15967,7 +15967,7 @@
         <v>0.57777999999999996</v>
       </c>
     </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>96</v>
       </c>
@@ -15987,7 +15987,7 @@
         <v>9.1299999999999992E-3</v>
       </c>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>96</v>
       </c>
@@ -16007,7 +16007,7 @@
         <v>0.11395</v>
       </c>
     </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>96</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>3.4619999999999998E-2</v>
       </c>
     </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>96</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>2.9510000000000002E-2</v>
       </c>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>96</v>
       </c>
@@ -16067,7 +16067,7 @@
         <v>2.8170000000000001E-2</v>
       </c>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A762">
         <v>96</v>
       </c>
@@ -16087,7 +16087,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>96</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>2.418E-2</v>
       </c>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>96</v>
       </c>
@@ -16127,7 +16127,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>96</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>1.651E-2</v>
       </c>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>96</v>
       </c>
@@ -16167,7 +16167,7 @@
         <v>1.21E-2</v>
       </c>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>96</v>
       </c>
@@ -16187,7 +16187,7 @@
         <v>1.448E-2</v>
       </c>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>96</v>
       </c>
@@ -16207,7 +16207,7 @@
         <v>7.9699999999999997E-3</v>
       </c>
     </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>96</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>8.9300000000000004E-3</v>
       </c>
     </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A770">
         <v>96</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>4.3899999999999998E-3</v>
       </c>
     </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A771">
         <v>96</v>
       </c>
@@ -16267,7 +16267,7 @@
         <v>5.0099999999999997E-3</v>
       </c>
     </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>96</v>
       </c>
@@ -16287,7 +16287,7 @@
         <v>3.1900000000000001E-3</v>
       </c>
     </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A773">
         <v>96</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>6.2100000000000002E-3</v>
       </c>
     </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>97</v>
       </c>
@@ -16327,7 +16327,7 @@
         <v>5.1799999999999997E-3</v>
       </c>
     </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>97</v>
       </c>
@@ -16347,7 +16347,7 @@
         <v>5.1799999999999997E-3</v>
       </c>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>293</v>
       </c>
@@ -16367,7 +16367,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>293</v>
       </c>
@@ -16387,7 +16387,7 @@
         <v>8.2350000000000007E-2</v>
       </c>
     </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>293</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>5.5379999999999999E-2</v>
       </c>
     </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>293</v>
       </c>
@@ -16427,7 +16427,7 @@
         <v>3.8460000000000001E-2</v>
       </c>
     </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>293</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>2.7779999999999999E-2</v>
       </c>
     </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A781">
         <v>293</v>
       </c>
@@ -16467,7 +16467,7 @@
         <v>2.1739999999999999E-2</v>
       </c>
     </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A782">
         <v>293</v>
       </c>
@@ -16487,7 +16487,7 @@
         <v>2.4029999999999999E-2</v>
       </c>
     </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A783">
         <v>293</v>
       </c>
@@ -16507,7 +16507,7 @@
         <v>1.566E-2</v>
       </c>
     </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A784">
         <v>293</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>1.6820000000000002E-2</v>
       </c>
     </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>293</v>
       </c>
@@ -16547,7 +16547,7 @@
         <v>1.538E-2</v>
       </c>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>293</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>1.333E-2</v>
       </c>
     </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A787">
         <v>293</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>1.5389999999999999E-2</v>
       </c>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A788">
         <v>293</v>
       </c>
@@ -16607,7 +16607,7 @@
         <v>1.2370000000000001E-2</v>
       </c>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A789">
         <v>293</v>
       </c>
@@ -16627,7 +16627,7 @@
         <v>9.8899999999999995E-3</v>
       </c>
     </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A790">
         <v>293</v>
       </c>
@@ -16647,7 +16647,7 @@
         <v>1.333E-2</v>
       </c>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A791">
         <v>293</v>
       </c>
@@ -16667,7 +16667,7 @@
         <v>9.5300000000000003E-3</v>
       </c>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A792">
         <v>293</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>1.18E-2</v>
       </c>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A793">
         <v>293</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A794">
         <v>293</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>1.034E-2</v>
       </c>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A795">
         <v>293</v>
       </c>
@@ -16747,7 +16747,7 @@
         <v>1.014E-2</v>
       </c>
     </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A796">
         <v>293</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>1.051E-2</v>
       </c>
     </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A797">
         <v>293</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>8.9200000000000008E-3</v>
       </c>
     </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A798">
         <v>293</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>5.9800000000000001E-3</v>
       </c>
     </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A799">
         <v>293</v>
       </c>
@@ -16827,7 +16827,7 @@
         <v>5.9800000000000001E-3</v>
       </c>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A800">
         <v>291</v>
       </c>
@@ -16847,7 +16847,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A801">
         <v>291</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>3.5714299999999999</v>
       </c>
     </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A802">
         <v>291</v>
       </c>
@@ -16887,7 +16887,7 @@
         <v>3.88889</v>
       </c>
     </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A803">
         <v>291</v>
       </c>
@@ -16907,7 +16907,7 @@
         <v>0.45833000000000002</v>
       </c>
     </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A804">
         <v>291</v>
       </c>
@@ -16927,7 +16927,7 @@
         <v>0.14917</v>
       </c>
     </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A805">
         <v>291</v>
       </c>
@@ -16947,7 +16947,7 @@
         <v>7.732E-2</v>
       </c>
     </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A806">
         <v>291</v>
       </c>
@@ -16967,7 +16967,7 @@
         <v>5.391E-2</v>
       </c>
     </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A807">
         <v>291</v>
       </c>
@@ -16987,7 +16987,7 @@
         <v>4.9070000000000003E-2</v>
       </c>
     </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A808">
         <v>291</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>3.5029999999999999E-2</v>
       </c>
     </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A809">
         <v>291</v>
       </c>
@@ -17027,7 +17027,7 @@
         <v>3.5029999999999999E-2</v>
       </c>
     </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A810">
         <v>286</v>
       </c>
@@ -17047,7 +17047,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A811">
         <v>286</v>
       </c>
@@ -17067,7 +17067,7 @@
         <v>4.5161E-2</v>
       </c>
     </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A812">
         <v>286</v>
       </c>
@@ -17087,7 +17087,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A813">
         <v>286</v>
       </c>
@@ -17107,7 +17107,7 @@
         <v>4.9057000000000003E-2</v>
       </c>
     </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A814">
         <v>286</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>4.1818000000000001E-2</v>
       </c>
     </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A815">
         <v>286</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>3.6666999999999998E-2</v>
       </c>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A816">
         <v>286</v>
       </c>
@@ -17167,7 +17167,7 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A817">
         <v>286</v>
       </c>
@@ -17187,7 +17187,7 @@
         <v>2.7616999999999999E-2</v>
       </c>
     </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A818">
         <v>286</v>
       </c>
@@ -17207,7 +17207,7 @@
         <v>2.4399000000000001E-2</v>
       </c>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A819">
         <v>286</v>
       </c>
@@ -17227,7 +17227,7 @@
         <v>2.1828E-2</v>
       </c>
     </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A820">
         <v>286</v>
       </c>
@@ -17247,7 +17247,7 @@
         <v>1.9689999999999999E-2</v>
       </c>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A821">
         <v>286</v>
       </c>
@@ -17267,7 +17267,7 @@
         <v>1.804E-2</v>
       </c>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A822">
         <v>286</v>
       </c>
@@ -17287,7 +17287,7 @@
         <v>1.6462000000000001E-2</v>
       </c>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A823">
         <v>286</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>1.5203E-2</v>
       </c>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A824">
         <v>286</v>
       </c>
@@ -17327,7 +17327,7 @@
         <v>1.4165000000000001E-2</v>
       </c>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A825">
         <v>286</v>
       </c>
@@ -17347,7 +17347,7 @@
         <v>1.5242E-2</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A826">
         <v>286</v>
       </c>
@@ -17367,7 +17367,7 @@
         <v>1.5242E-2</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A827">
         <v>239</v>
       </c>
@@ -17387,7 +17387,7 @@
         <v>1.98807</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A828">
         <v>239</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>1.98807</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A829">
         <v>400</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A830">
         <v>400</v>
       </c>
@@ -17447,7 +17447,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A831">
         <v>400</v>
       </c>
@@ -17467,7 +17467,7 @@
         <v>3.8890000000000001E-2</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A832">
         <v>400</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A833">
         <v>400</v>
       </c>
@@ -17507,7 +17507,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A834">
         <v>400</v>
       </c>
@@ -17527,7 +17527,7 @@
         <v>1.4250000000000001E-2</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A835">
         <v>400</v>
       </c>
@@ -17547,7 +17547,7 @@
         <v>1.1780000000000001E-2</v>
       </c>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A836">
         <v>400</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>8.4600000000000005E-3</v>
       </c>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A837">
         <v>400</v>
       </c>
@@ -17587,7 +17587,7 @@
         <v>9.2300000000000004E-3</v>
       </c>
     </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A838">
         <v>400</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>7.2199999999999999E-3</v>
       </c>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A839">
         <v>400</v>
       </c>
@@ -17627,7 +17627,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A840">
         <v>400</v>
       </c>
@@ -17647,7 +17647,7 @@
         <v>8.3800000000000003E-3</v>
       </c>
     </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A841">
         <v>400</v>
       </c>
@@ -17667,7 +17667,7 @@
         <v>8.3800000000000003E-3</v>
       </c>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A842">
         <v>401</v>
       </c>
@@ -17687,7 +17687,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A843">
         <v>401</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A844">
         <v>401</v>
       </c>
@@ -17727,7 +17727,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A845">
         <v>401</v>
       </c>
@@ -17747,7 +17747,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A846">
         <v>401</v>
       </c>
@@ -17767,7 +17767,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A847">
         <v>401</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A848">
         <v>401</v>
       </c>
@@ -17807,7 +17807,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A849">
         <v>401</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A850">
         <v>401</v>
       </c>
@@ -17847,7 +17847,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A851">
         <v>401</v>
       </c>
@@ -17867,7 +17867,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A852">
         <v>401</v>
       </c>
@@ -17887,7 +17887,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A853">
         <v>422</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A854">
         <v>422</v>
       </c>
@@ -17927,7 +17927,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A855">
         <v>422</v>
       </c>
@@ -17947,7 +17947,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A856">
         <v>422</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A857">
         <v>422</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A858">
         <v>422</v>
       </c>
@@ -18007,7 +18007,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A859">
         <v>422</v>
       </c>
@@ -18027,7 +18027,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A860">
         <v>422</v>
       </c>
@@ -18047,7 +18047,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A861">
         <v>422</v>
       </c>
@@ -18067,7 +18067,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A862">
         <v>500</v>
       </c>
@@ -18087,7 +18087,7 @@
         <v>0.33683999999999997</v>
       </c>
     </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A863">
         <v>500</v>
       </c>
@@ -18107,7 +18107,7 @@
         <v>0.20694000000000001</v>
       </c>
     </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A864">
         <v>500</v>
       </c>
@@ -18127,7 +18127,7 @@
         <v>9.6640000000000004E-2</v>
       </c>
     </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A865">
         <v>500</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>0.11559999999999999</v>
       </c>
     </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A866">
         <v>500</v>
       </c>
@@ -18167,7 +18167,7 @@
         <v>0.16236</v>
       </c>
     </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A867">
         <v>500</v>
       </c>
@@ -18187,7 +18187,7 @@
         <v>6.9349999999999995E-2</v>
       </c>
     </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A868">
         <v>500</v>
       </c>
@@ -18207,7 +18207,7 @@
         <v>4.6940000000000003E-2</v>
       </c>
     </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A869">
         <v>500</v>
       </c>
@@ -18227,7 +18227,7 @@
         <v>3.916E-2</v>
       </c>
     </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A870">
         <v>500</v>
       </c>
@@ -18247,7 +18247,7 @@
         <v>1.7330000000000002E-2</v>
       </c>
     </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A871">
         <v>500</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>1.489E-2</v>
       </c>
     </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A872">
         <v>500</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>1.1339999999999999E-2</v>
       </c>
     </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A873">
         <v>500</v>
       </c>
@@ -18307,7 +18307,7 @@
         <v>1.1339999999999999E-2</v>
       </c>
     </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A874">
         <v>500</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>9.58E-3</v>
       </c>
     </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A875">
         <v>500</v>
       </c>
@@ -18347,7 +18347,7 @@
         <v>1.026E-2</v>
       </c>
     </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A876">
         <v>500</v>
       </c>
@@ -18367,7 +18367,7 @@
         <v>2.2589999999999999E-2</v>
       </c>
     </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A877">
         <v>500</v>
       </c>
@@ -18387,7 +18387,7 @@
         <v>1.128E-2</v>
       </c>
     </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A878">
         <v>500</v>
       </c>
@@ -18407,7 +18407,7 @@
         <v>1.128E-2</v>
       </c>
     </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A879">
         <v>500</v>
       </c>
@@ -18427,7 +18427,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A880">
         <v>500</v>
       </c>
@@ -18447,7 +18447,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A881">
         <v>500</v>
       </c>
@@ -18467,7 +18467,7 @@
         <v>1.37E-2</v>
       </c>
     </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A882">
         <v>500</v>
       </c>
@@ -18487,7 +18487,7 @@
         <v>1.37E-2</v>
       </c>
     </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A883">
         <v>500</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>1.242E-2</v>
       </c>
     </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A884">
         <v>500</v>
       </c>
@@ -18527,7 +18527,7 @@
         <v>1.242E-2</v>
       </c>
     </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A885">
         <v>500</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>1.239E-2</v>
       </c>
     </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A886">
         <v>500</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>1.239E-2</v>
       </c>
     </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A887">
         <v>500</v>
       </c>
@@ -18587,7 +18587,7 @@
         <v>1.1140000000000001E-2</v>
       </c>
     </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A888">
         <v>500</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>1.1140000000000001E-2</v>
       </c>
     </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A889">
         <v>500</v>
       </c>
@@ -18627,7 +18627,7 @@
         <v>1.11E-2</v>
       </c>
     </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A890">
         <v>500</v>
       </c>
@@ -18647,7 +18647,7 @@
         <v>1.11E-2</v>
       </c>
     </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A891">
         <v>500</v>
       </c>
@@ -18667,7 +18667,7 @@
         <v>1.108E-2</v>
       </c>
     </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A892">
         <v>500</v>
       </c>
@@ -18687,7 +18687,7 @@
         <v>1.108E-2</v>
       </c>
     </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A893">
         <v>500</v>
       </c>
@@ -18707,7 +18707,7 @@
         <v>1.106E-2</v>
       </c>
     </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A894">
         <v>500</v>
       </c>
@@ -18727,7 +18727,7 @@
         <v>1.106E-2</v>
       </c>
     </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A895">
         <v>500</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>7.3499999999999998E-3</v>
       </c>
     </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A896">
         <v>500</v>
       </c>
@@ -18767,7 +18767,7 @@
         <v>7.3499999999999998E-3</v>
       </c>
     </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A897">
         <v>500</v>
       </c>
@@ -18787,7 +18787,7 @@
         <v>1.102E-2</v>
       </c>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A898">
         <v>500</v>
       </c>
@@ -18807,7 +18807,7 @@
         <v>1.102E-2</v>
       </c>
     </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A899">
         <v>500</v>
       </c>
@@ -18827,7 +18827,7 @@
         <v>7.3299999999999997E-3</v>
       </c>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A900">
         <v>500</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>7.3299999999999997E-3</v>
       </c>
     </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A901">
         <v>500</v>
       </c>
@@ -18867,7 +18867,7 @@
         <v>1.0959999999999999E-2</v>
       </c>
     </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A902">
         <v>500</v>
       </c>
@@ -18887,7 +18887,7 @@
         <v>1.0959999999999999E-2</v>
       </c>
     </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A903">
         <v>500</v>
       </c>
@@ -18907,7 +18907,7 @@
         <v>7.3099999999999997E-3</v>
       </c>
     </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A904">
         <v>500</v>
       </c>
@@ -18927,7 +18927,7 @@
         <v>7.3099999999999997E-3</v>
       </c>
     </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A905">
         <v>500</v>
       </c>
@@ -18947,7 +18947,7 @@
         <v>6.0800000000000003E-3</v>
       </c>
     </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A906">
         <v>500</v>
       </c>
@@ -18967,7 +18967,7 @@
         <v>6.0800000000000003E-3</v>
       </c>
     </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A907">
         <v>500</v>
       </c>
@@ -18987,7 +18987,7 @@
         <v>6.0699999999999999E-3</v>
       </c>
     </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A908">
         <v>500</v>
       </c>
@@ -19007,7 +19007,7 @@
         <v>6.0699999999999999E-3</v>
       </c>
     </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A909">
         <v>500</v>
       </c>
@@ -19027,7 +19027,7 @@
         <v>7.28E-3</v>
       </c>
     </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A910">
         <v>500</v>
       </c>
@@ -19047,7 +19047,7 @@
         <v>7.28E-3</v>
       </c>
     </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A911">
         <v>500</v>
       </c>
@@ -19067,7 +19067,7 @@
         <v>6.0499999999999998E-3</v>
       </c>
     </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A912">
         <v>500</v>
       </c>
@@ -19087,7 +19087,7 @@
         <v>6.0499999999999998E-3</v>
       </c>
     </row>
-    <row r="913" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A913">
         <v>500</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
-    <row r="914" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A914">
         <v>500</v>
       </c>
@@ -19127,7 +19127,7 @@
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A915">
         <v>500</v>
       </c>
@@ -19147,7 +19147,7 @@
         <v>1.566E-2</v>
       </c>
     </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A916">
         <v>500</v>
       </c>
@@ -19167,7 +19167,7 @@
         <v>1.566E-2</v>
       </c>
     </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A917">
         <v>500</v>
       </c>
@@ -19187,7 +19187,7 @@
         <v>1.5610000000000001E-2</v>
       </c>
     </row>
-    <row r="918" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A918">
         <v>500</v>
       </c>
@@ -19207,7 +19207,7 @@
         <v>1.5610000000000001E-2</v>
       </c>
     </row>
-    <row r="919" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A919">
         <v>500</v>
       </c>
@@ -19227,7 +19227,7 @@
         <v>1.3169999999999999E-2</v>
       </c>
     </row>
-    <row r="920" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A920">
         <v>500</v>
       </c>
@@ -19247,7 +19247,7 @@
         <v>1.3169999999999999E-2</v>
       </c>
     </row>
-    <row r="921" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A921">
         <v>500</v>
       </c>
@@ -19267,7 +19267,7 @@
         <v>1.5509999999999999E-2</v>
       </c>
     </row>
-    <row r="922" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A922">
         <v>500</v>
       </c>
@@ -19287,7 +19287,7 @@
         <v>1.5509999999999999E-2</v>
       </c>
     </row>
-    <row r="923" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A923">
         <v>500</v>
       </c>
@@ -19307,7 +19307,7 @@
         <v>1.7840000000000002E-2</v>
       </c>
     </row>
-    <row r="924" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A924">
         <v>500</v>
       </c>
@@ -19327,7 +19327,7 @@
         <v>1.7840000000000002E-2</v>
       </c>
     </row>
-    <row r="925" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A925">
         <v>500</v>
       </c>
@@ -19347,7 +19347,7 @@
         <v>1.7809999999999999E-2</v>
       </c>
     </row>
-    <row r="926" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A926">
         <v>500</v>
       </c>
@@ -19367,7 +19367,7 @@
         <v>1.7770000000000001E-2</v>
       </c>
     </row>
-    <row r="927" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A927">
         <v>500</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>1.771E-2</v>
       </c>
     </row>
-    <row r="928" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A928">
         <v>500</v>
       </c>
@@ -19407,7 +19407,7 @@
         <v>1.771E-2</v>
       </c>
     </row>
-    <row r="929" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A929">
         <v>500</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>1.6490000000000001E-2</v>
       </c>
     </row>
-    <row r="930" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A930">
         <v>500</v>
       </c>
@@ -19447,7 +19447,7 @@
         <v>1.6490000000000001E-2</v>
       </c>
     </row>
-    <row r="931" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A931">
         <v>500</v>
       </c>
@@ -19467,7 +19467,7 @@
         <v>1.8780000000000002E-2</v>
       </c>
     </row>
-    <row r="932" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A932">
         <v>500</v>
       </c>
@@ -19487,7 +19487,7 @@
         <v>1.8780000000000002E-2</v>
       </c>
     </row>
-    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A933">
         <v>500</v>
       </c>
@@ -19507,7 +19507,7 @@
         <v>1.4019999999999999E-2</v>
       </c>
     </row>
-    <row r="934" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A934">
         <v>500</v>
       </c>
@@ -19527,7 +19527,7 @@
         <v>1.4019999999999999E-2</v>
       </c>
     </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A935">
         <v>500</v>
       </c>
@@ -19547,7 +19547,7 @@
         <v>1.634E-2</v>
       </c>
     </row>
-    <row r="936" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A936">
         <v>500</v>
       </c>
@@ -19567,7 +19567,7 @@
         <v>1.634E-2</v>
       </c>
     </row>
-    <row r="937" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A937">
         <v>500</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>1.7420000000000001E-2</v>
       </c>
     </row>
-    <row r="938" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A938">
         <v>500</v>
       </c>
@@ -19607,7 +19607,7 @@
         <v>1.7420000000000001E-2</v>
       </c>
     </row>
-    <row r="939" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A939">
         <v>500</v>
       </c>
@@ -19627,7 +19627,7 @@
         <v>1.8519999999999998E-2</v>
       </c>
     </row>
-    <row r="940" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A940">
         <v>500</v>
       </c>
@@ -19647,7 +19647,7 @@
         <v>1.8519999999999998E-2</v>
       </c>
     </row>
-    <row r="941" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A941">
         <v>500</v>
       </c>
@@ -19667,7 +19667,7 @@
         <v>1.6150000000000001E-2</v>
       </c>
     </row>
-    <row r="942" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A942">
         <v>500</v>
       </c>
@@ -19687,7 +19687,7 @@
         <v>1.6150000000000001E-2</v>
       </c>
     </row>
-    <row r="943" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A943">
         <v>500</v>
       </c>
@@ -19707,7 +19707,7 @@
         <v>2.0729999999999998E-2</v>
       </c>
     </row>
-    <row r="944" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A944">
         <v>500</v>
       </c>
@@ -19727,7 +19727,7 @@
         <v>2.069E-2</v>
       </c>
     </row>
-    <row r="945" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A945">
         <v>500</v>
       </c>
@@ -19747,7 +19747,7 @@
         <v>1.376E-2</v>
       </c>
     </row>
-    <row r="946" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A946">
         <v>500</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>1.376E-2</v>
       </c>
     </row>
-    <row r="947" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A947">
         <v>500</v>
       </c>
@@ -19787,7 +19787,7 @@
         <v>1.482E-2</v>
       </c>
     </row>
-    <row r="948" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A948">
         <v>500</v>
       </c>
@@ -19807,7 +19807,7 @@
         <v>1.482E-2</v>
       </c>
     </row>
-    <row r="949" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A949">
         <v>500</v>
       </c>
@@ -19827,7 +19827,7 @@
         <v>1.367E-2</v>
       </c>
     </row>
-    <row r="950" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A950">
         <v>500</v>
       </c>
@@ -19847,7 +19847,7 @@
         <v>1.367E-2</v>
       </c>
     </row>
-    <row r="951" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A951">
         <v>500</v>
       </c>
@@ -19867,7 +19867,7 @@
         <v>1.362E-2</v>
       </c>
     </row>
-    <row r="952" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A952">
         <v>500</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>1.362E-2</v>
       </c>
     </row>
-    <row r="953" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A953">
         <v>500</v>
       </c>
@@ -19907,7 +19907,7 @@
         <v>1.247E-2</v>
       </c>
     </row>
-    <row r="954" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A954">
         <v>500</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>1.247E-2</v>
       </c>
     </row>
-    <row r="955" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A955">
         <v>500</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>1.1299999999999999E-2</v>
       </c>
     </row>
-    <row r="956" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A956">
         <v>500</v>
       </c>
@@ -19967,7 +19967,7 @@
         <v>1.1299999999999999E-2</v>
       </c>
     </row>
-    <row r="957" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A957">
         <v>500</v>
       </c>
@@ -19987,7 +19987,7 @@
         <v>1.0149999999999999E-2</v>
       </c>
     </row>
-    <row r="958" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A958">
         <v>500</v>
       </c>
@@ -20007,7 +20007,7 @@
         <v>1.0149999999999999E-2</v>
       </c>
     </row>
-    <row r="959" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A959">
         <v>500</v>
       </c>
@@ -20027,7 +20027,7 @@
         <v>9.0100000000000006E-3</v>
       </c>
     </row>
-    <row r="960" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A960">
         <v>500</v>
       </c>
@@ -20047,7 +20047,7 @@
         <v>9.0100000000000006E-3</v>
       </c>
     </row>
-    <row r="961" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A961">
         <v>500</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>1.1220000000000001E-2</v>
       </c>
     </row>
-    <row r="962" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A962">
         <v>500</v>
       </c>
@@ -20087,7 +20087,7 @@
         <v>1.1220000000000001E-2</v>
       </c>
     </row>
-    <row r="963" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A963">
         <v>500</v>
       </c>
@@ -20107,7 +20107,7 @@
         <v>1.009E-2</v>
       </c>
     </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A964">
         <v>500</v>
       </c>
@@ -20127,7 +20127,7 @@
         <v>1.009E-2</v>
       </c>
     </row>
-    <row r="965" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A965">
         <v>500</v>
       </c>
@@ -20147,7 +20147,7 @@
         <v>1.119E-2</v>
       </c>
     </row>
-    <row r="966" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A966">
         <v>500</v>
       </c>
@@ -20167,7 +20167,7 @@
         <v>1.119E-2</v>
       </c>
     </row>
-    <row r="967" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A967">
         <v>500</v>
       </c>
@@ -20187,7 +20187,7 @@
         <v>8.94E-3</v>
       </c>
     </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A968">
         <v>500</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>8.94E-3</v>
       </c>
     </row>
-    <row r="969" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A969">
         <v>500</v>
       </c>
@@ -20227,7 +20227,7 @@
         <v>1.0019999999999999E-2</v>
       </c>
     </row>
-    <row r="970" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A970">
         <v>500</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>1.0019999999999999E-2</v>
       </c>
     </row>
-    <row r="971" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A971">
         <v>500</v>
       </c>
@@ -20267,7 +20267,7 @@
         <v>1.001E-2</v>
       </c>
     </row>
-    <row r="972" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A972">
         <v>500</v>
       </c>
@@ -20287,7 +20287,7 @@
         <v>1.001E-2</v>
       </c>
     </row>
-    <row r="973" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A973">
         <v>500</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>1.001E-2</v>
       </c>
     </row>
-    <row r="974" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A974">
         <v>500</v>
       </c>
@@ -20327,7 +20327,7 @@
         <v>1.001E-2</v>
       </c>
     </row>
-    <row r="975" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A975">
         <v>500</v>
       </c>
@@ -20347,7 +20347,7 @@
         <v>1.001E-2</v>
       </c>
     </row>
-    <row r="976" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A976">
         <v>501</v>
       </c>
@@ -20367,7 +20367,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="977" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A977">
         <v>501</v>
       </c>
@@ -20387,7 +20387,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="978" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A978">
         <v>501</v>
       </c>
@@ -20407,7 +20407,7 @@
         <v>9.9379999999999996E-2</v>
       </c>
     </row>
-    <row r="979" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A979">
         <v>501</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>6.0109999999999997E-2</v>
       </c>
     </row>
-    <row r="980" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A980">
         <v>501</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>5.0599999999999999E-2</v>
       </c>
     </row>
-    <row r="981" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A981">
         <v>501</v>
       </c>
@@ -20467,7 +20467,7 @@
         <v>3.5450000000000002E-2</v>
       </c>
     </row>
-    <row r="982" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A982">
         <v>501</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>1.507E-2</v>
       </c>
     </row>
-    <row r="983" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A983">
         <v>501</v>
       </c>
@@ -20507,7 +20507,7 @@
         <v>3.9019999999999999E-2</v>
       </c>
     </row>
-    <row r="984" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A984">
         <v>501</v>
       </c>
@@ -20527,7 +20527,7 @@
         <v>7.3699999999999998E-3</v>
       </c>
     </row>
-    <row r="985" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A985">
         <v>501</v>
       </c>
@@ -20547,7 +20547,7 @@
         <v>1.238E-2</v>
       </c>
     </row>
-    <row r="986" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A986">
         <v>501</v>
       </c>
@@ -20567,7 +20567,7 @@
         <v>1.9570000000000001E-2</v>
       </c>
     </row>
-    <row r="987" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A987">
         <v>501</v>
       </c>
@@ -20587,7 +20587,7 @@
         <v>2.4119999999999999E-2</v>
       </c>
     </row>
-    <row r="988" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A988">
         <v>501</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>1.753E-2</v>
       </c>
     </row>
-    <row r="989" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A989">
         <v>501</v>
       </c>
@@ -20627,7 +20627,7 @@
         <v>1.447E-2</v>
       </c>
     </row>
-    <row r="990" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A990">
         <v>501</v>
       </c>
@@ -20647,7 +20647,7 @@
         <v>1.119E-2</v>
       </c>
     </row>
-    <row r="991" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A991">
         <v>501</v>
       </c>
@@ -20667,7 +20667,7 @@
         <v>1.115E-2</v>
       </c>
     </row>
-    <row r="992" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A992">
         <v>501</v>
       </c>
@@ -20687,7 +20687,7 @@
         <v>8.4600000000000005E-3</v>
       </c>
     </row>
-    <row r="993" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A993">
         <v>501</v>
       </c>
@@ -20707,7 +20707,7 @@
         <v>6.3200000000000001E-3</v>
       </c>
     </row>
-    <row r="994" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A994">
         <v>501</v>
       </c>
@@ -20727,7 +20727,7 @@
         <v>5.5900000000000004E-3</v>
       </c>
     </row>
-    <row r="995" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A995">
         <v>501</v>
       </c>
@@ -20747,7 +20747,7 @@
         <v>5.5799999999999999E-3</v>
       </c>
     </row>
-    <row r="996" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A996">
         <v>501</v>
       </c>
@@ -20767,7 +20767,7 @@
         <v>5.5799999999999999E-3</v>
       </c>
     </row>
-    <row r="997" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A997">
         <v>600</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>1.6959999999999999E-2</v>
       </c>
     </row>
-    <row r="998" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A998">
         <v>600</v>
       </c>
@@ -20807,7 +20807,7 @@
         <v>1.6959999999999999E-2</v>
       </c>
     </row>
-    <row r="999" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A999">
         <v>999</v>
       </c>
@@ -20818,7 +20818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1000" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1000">
         <v>999</v>
       </c>
@@ -20829,7 +20829,7 @@
         <v>326.2</v>
       </c>
     </row>
-    <row r="1001" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -20840,7 +20840,7 @@
         <v>369.2</v>
       </c>
     </row>
-    <row r="1002" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1002">
         <v>999</v>
       </c>
@@ -20851,7 +20851,7 @@
         <v>399.6</v>
       </c>
     </row>
-    <row r="1003" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1003">
         <v>999</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>426.6</v>
       </c>
     </row>
-    <row r="1004" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1004">
         <v>999</v>
       </c>
@@ -20873,7 +20873,7 @@
         <v>452.8</v>
       </c>
     </row>
-    <row r="1005" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1005">
         <v>999</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>490.5</v>
       </c>
     </row>
-    <row r="1006" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1006">
         <v>999</v>
       </c>
@@ -20895,7 +20895,7 @@
         <v>516.4</v>
       </c>
     </row>
-    <row r="1007" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1007">
         <v>999</v>
       </c>
@@ -20906,7 +20906,7 @@
         <v>532.79999999999995</v>
       </c>
     </row>
-    <row r="1008" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1008">
         <v>999</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>548.70000000000005</v>
       </c>
     </row>
-    <row r="1009" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1009">
         <v>999</v>
       </c>
@@ -20938,14 +20938,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60F64A3-D3E9-48DB-B897-E9AAD6863BCB}">
   <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -20956,7 +20956,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -20967,7 +20967,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -20994,7 +20994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -21005,7 +21005,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -21013,7 +21013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -21032,7 +21032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -21043,7 +21043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -21065,7 +21065,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -21073,7 +21073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>15</v>
       </c>
@@ -21081,7 +21081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -21089,7 +21089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>17</v>
       </c>
@@ -21097,7 +21097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>18</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>19</v>
       </c>
@@ -21116,7 +21116,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>20</v>
       </c>
@@ -21124,7 +21124,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>21</v>
       </c>
@@ -21132,7 +21132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>22</v>
       </c>
@@ -21140,7 +21140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>23</v>
       </c>
@@ -21148,7 +21148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>24</v>
       </c>
@@ -21156,7 +21156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25</v>
       </c>
@@ -21164,7 +21164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26</v>
       </c>
@@ -21172,7 +21172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>27</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>28</v>
       </c>
@@ -21188,7 +21188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>29</v>
       </c>
@@ -21196,7 +21196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>30</v>
       </c>
@@ -21204,7 +21204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>31</v>
       </c>
@@ -21212,7 +21212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>32</v>
       </c>
@@ -21220,7 +21220,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>33</v>
       </c>
@@ -21228,7 +21228,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>34</v>
       </c>
@@ -21236,7 +21236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>35</v>
       </c>
@@ -21244,7 +21244,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>36</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>37</v>
       </c>
@@ -21260,7 +21260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>40</v>
       </c>
@@ -21268,7 +21268,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>41</v>
       </c>
@@ -21276,7 +21276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>42</v>
       </c>
@@ -21284,7 +21284,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>44</v>
       </c>
@@ -21292,7 +21292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>45</v>
       </c>
@@ -21300,7 +21300,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>52</v>
       </c>
@@ -21308,7 +21308,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>53</v>
       </c>
@@ -21316,7 +21316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>63</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>74</v>
       </c>
@@ -21332,7 +21332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>75</v>
       </c>
@@ -21340,7 +21340,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>76</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>78</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>79</v>
       </c>
@@ -21364,7 +21364,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>81</v>
       </c>
@@ -21372,7 +21372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>90</v>
       </c>
@@ -21380,7 +21380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>91</v>
       </c>
@@ -21388,7 +21388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>92</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>93</v>
       </c>
@@ -21404,7 +21404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>94</v>
       </c>
@@ -21412,7 +21412,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>95</v>
       </c>
@@ -21420,7 +21420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>96</v>
       </c>
@@ -21428,7 +21428,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>97</v>
       </c>
@@ -21436,7 +21436,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>293</v>
       </c>
@@ -21444,7 +21444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>291</v>
       </c>
@@ -21452,7 +21452,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>286</v>
       </c>
@@ -21460,7 +21460,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>239</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>400</v>
       </c>
@@ -21476,7 +21476,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>401</v>
       </c>
@@ -21484,7 +21484,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>422</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>500</v>
       </c>
@@ -21500,7 +21500,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>501</v>
       </c>
@@ -21508,7 +21508,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>999</v>
       </c>
